--- a/project_documents/Sprint Retrospective.xlsx
+++ b/project_documents/Sprint Retrospective.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\LLM-Evaluation-system\project_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8738B87C-B96E-4D3C-880A-A7BFF1FE1A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F50BFF9-A9A4-4180-A9A8-0986BB1F654E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{911B58EC-8885-4802-ACFC-2893CF45B98D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="63">
   <si>
     <t>Sprint #</t>
   </si>
@@ -150,6 +150,81 @@
   </si>
   <si>
     <t>Generate embeddings using SentenceTransformer</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
+  </si>
+  <si>
+    <t>Develop Accuracy Agent</t>
+  </si>
+  <si>
+    <t>Manual response checking</t>
+  </si>
+  <si>
+    <t>Improve evaluation quality</t>
+  </si>
+  <si>
+    <t>Implemented Accuracy Agent</t>
+  </si>
+  <si>
+    <t>Develop Relevance Agent</t>
+  </si>
+  <si>
+    <t>Simple keyword matching</t>
+  </si>
+  <si>
+    <t>Improve semantic evaluation</t>
+  </si>
+  <si>
+    <t>Implemented Relevance Agent</t>
+  </si>
+  <si>
+    <t>Develop Hallucination Agent</t>
+  </si>
+  <si>
+    <t>Manual hallucination detection</t>
+  </si>
+  <si>
+    <t>Improve AI validation</t>
+  </si>
+  <si>
+    <t>Implemented Hallucination Agent</t>
+  </si>
+  <si>
+    <t>Improve evaluation dashboard</t>
+  </si>
+  <si>
+    <t>Basic UI layout</t>
+  </si>
+  <si>
+    <t>Enhance user interface</t>
+  </si>
+  <si>
+    <t>Created evaluation dashboard</t>
+  </si>
+  <si>
+    <t>Integrate Judge Agents</t>
+  </si>
+  <si>
+    <t>Separate evaluation modules</t>
+  </si>
+  <si>
+    <t>Improve integration</t>
+  </si>
+  <si>
+    <t>Integrated all Judge Agents</t>
+  </si>
+  <si>
+    <t>Perform complete testing</t>
+  </si>
+  <si>
+    <t>Partial testing</t>
+  </si>
+  <si>
+    <t>Validate system performance</t>
+  </si>
+  <si>
+    <t>Completed Milestone 2 testing</t>
   </si>
 </sst>
 </file>
@@ -204,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -223,6 +298,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE708F5-F36F-4432-BB0A-7B4053099079}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.36328125" style="1" customWidth="1"/>
@@ -579,7 +657,7 @@
     <col min="8" max="8" width="29.08984375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -605,7 +683,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -631,7 +709,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -657,7 +735,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -683,7 +761,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -709,7 +787,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -735,7 +813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -761,7 +839,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -785,6 +863,162 @@
       </c>
       <c r="H8" s="6" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46213</v>
+      </c>
+      <c r="C9" s="5">
+        <v>46222</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46213</v>
+      </c>
+      <c r="C10" s="5">
+        <v>46222</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46213</v>
+      </c>
+      <c r="C11" s="5">
+        <v>46222</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46213</v>
+      </c>
+      <c r="C12" s="5">
+        <v>46222</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46213</v>
+      </c>
+      <c r="C13" s="5">
+        <v>46222</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46213</v>
+      </c>
+      <c r="C14" s="5">
+        <v>46222</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
